--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487812_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487812_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8738</v>
+        <v>5.4808</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4746</v>
+        <v>4.0815</v>
       </c>
       <c r="F2" t="n">
         <v>1.3993</v>
@@ -610,10 +610,10 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0779</v>
+        <v>0.6848</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3975</v>
+        <v>1.0045</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3196</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9766</v>
+        <v>1.7329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8122</v>
+        <v>0.5979</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1643</v>
+        <v>1.135</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7087</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9558</v>
+        <v>0.7121</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1149</v>
+        <v>0.9006</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1591</v>
+        <v>-0.1885</v>
       </c>
       <c r="V3" t="n">
         <v>1.5213</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4535</v>
+        <v>0.3959</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7289</v>
+        <v>0.4872</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2754</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5735</v>
+        <v>2.6097</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4201</v>
+        <v>1.7337</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9936</v>
+        <v>0.876</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3654</v>
+        <v>3.6713</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3262</v>
+        <v>2.5137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0392</v>
+        <v>1.1577</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9389</v>
+        <v>-1.0616</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0939</v>
+        <v>-0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0328</v>
+        <v>-0.2817</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4027</v>
+        <v>0.0349</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3635</v>
+        <v>0.1458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0391</v>
+        <v>-0.1109</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5838</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0964</v>
+        <v>-0.0027</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.7785</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0051</v>
+        <v>-0.7812</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4017</v>
+        <v>-0.406</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1919</v>
+        <v>-0.5839</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2098</v>
+        <v>0.178</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0392</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1919</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>0.3167</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4409</v>
+        <v>-0.9146</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1919</v>
+        <v>-0.7758</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.249</v>
+        <v>-0.1388</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1109</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1305</v>
+        <v>0.4968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0196</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1414</v>
+        <v>-0.067</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2729</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4143</v>
+        <v>0.0243</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6097</v>
+        <v>-0.4017</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7337</v>
+        <v>-0.1919</v>
       </c>
       <c r="I7" t="n">
-        <v>0.876</v>
+        <v>-0.2098</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6713</v>
+        <v>0.0392</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5137</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1577</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0616</v>
+        <v>-0.4409</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.78</v>
+        <v>-0.1919</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2817</v>
+        <v>-0.249</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5024</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1305</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4338</v>
+        <v>0.0489</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0514</v>
+        <v>-0.2379</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3583</v>
+        <v>0.9788</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6931</v>
+        <v>-1.2167</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.406</v>
+        <v>-0.5735</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5839</v>
+        <v>0.4201</v>
       </c>
       <c r="I8" t="n">
-        <v>0.178</v>
+        <v>-0.9936</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.3654</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1919</v>
+        <v>0.3262</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3167</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9146</v>
+        <v>-0.9389</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7758</v>
+        <v>0.0939</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1388</v>
+        <v>-1.0328</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1241</v>
+        <v>0.7113</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.64</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.484</v>
+        <v>0.0979</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3538</v>
+        <v>-0.5838</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6825</v>
+        <v>-0.9156</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6397</v>
+        <v>-0.9315</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0428</v>
+        <v>0.0159</v>
       </c>
       <c r="G9" t="n">
         <v>2.0834</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0791</v>
+        <v>-0.3122</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.901</v>
+        <v>-0.1928</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1781</v>
+        <v>-0.1193</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8137</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.53</v>
+        <v>-2.4122</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0121</v>
+        <v>-1.9825</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5178</v>
+        <v>-0.4297</v>
       </c>
       <c r="G10" t="n">
         <v>-3.511</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2676</v>
+        <v>-0.1499</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5748</v>
+        <v>0.4548</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6928</v>
+        <v>-0.6047</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7197</v>
+        <v>-4.2592</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7008</v>
+        <v>-3.0642</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0188</v>
+        <v>-1.195</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1765</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7274</v>
+        <v>0.1879</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5153</v>
+        <v>0.152</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2121</v>
+        <v>0.0359</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1298</v>
+        <v>-6.4359</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6487</v>
+        <v>-2.6906</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4811</v>
+        <v>-3.7453</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6157</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7992</v>
+        <v>0.493</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1769</v>
+        <v>1.1349</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3777</v>
+        <v>-0.6419</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6889</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.904400000000001</v>
+        <v>-6.577999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.162300000000001</v>
+        <v>-1.8362</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.7419</v>
+        <v>-4.7418</v>
       </c>
       <c r="G13" t="n">
         <v>-4.4906</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.306899999999999</v>
+        <v>-4.3069</v>
       </c>
       <c r="I13" t="n">
         <v>-0.1838000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>5.124599999999999</v>
+        <v>5.124600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.491900000000001</v>
+        <v>2.4919</v>
       </c>
       <c r="L13" t="n">
-        <v>2.632899999999999</v>
+        <v>2.6329</v>
       </c>
       <c r="M13" t="n">
         <v>-9.615200000000002</v>
@@ -1468,10 +1468,10 @@
         <v>13.5275</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8789</v>
+        <v>2.2049</v>
       </c>
       <c r="T13" t="n">
-        <v>4.253299999999999</v>
+        <v>4.579499999999999</v>
       </c>
       <c r="U13" t="n">
         <v>-2.3743</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.9575</v>
+        <v>7.7598</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7049</v>
+        <v>6.419</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2527</v>
+        <v>1.3407</v>
       </c>
       <c r="G14" t="n">
         <v>2.153</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1771</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5032</v>
+        <v>1.2173</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3261</v>
+        <v>-0.2381</v>
       </c>
       <c r="V14" t="n">
         <v>3.3787</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2847</v>
+        <v>4.2173</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9886</v>
+        <v>5.6316</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7039</v>
+        <v>-1.4143</v>
       </c>
       <c r="G15" t="n">
         <v>5.3761</v>
@@ -1624,13 +1624,13 @@
         <v>2.4974</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5748</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2252</v>
+        <v>-0.9355</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7076</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1909</v>
+        <v>2.2647</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.2181</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2228</v>
+        <v>2.0466</v>
       </c>
       <c r="G16" t="n">
         <v>0.3888</v>
@@ -1702,13 +1702,13 @@
         <v>2.7055</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8209</v>
+        <v>0.8946</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5931</v>
+        <v>0.843</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2278</v>
+        <v>0.0516</v>
       </c>
       <c r="V16" t="n">
         <v>1.3975</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7357</v>
+        <v>1.0737</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7488</v>
+        <v>-0.0013</v>
       </c>
       <c r="F17" t="n">
-        <v>0.987</v>
+        <v>1.075</v>
       </c>
       <c r="G17" t="n">
         <v>2.2984</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2916</v>
+        <v>-0.3704</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8416</v>
+        <v>0.0915</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4619</v>
       </c>
       <c r="V17" t="n">
         <v>-0.23</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1459</v>
+        <v>0.201</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1662</v>
+        <v>0.4876</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3121</v>
+        <v>-0.2866</v>
       </c>
       <c r="G18" t="n">
         <v>0.9943</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1808</v>
+        <v>-0.8339</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1057</v>
+        <v>0.2158</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0751</v>
+        <v>-1.0497</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5838</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4288</v>
+        <v>0.0062</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.336</v>
+        <v>-2.0146</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9072</v>
+        <v>2.0207</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8063</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7463</v>
+        <v>-0.3114</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1586</v>
+        <v>0.1629</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5878</v>
+        <v>-0.4743</v>
       </c>
       <c r="V19" t="n">
         <v>0.7076</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4103</v>
+        <v>-0.5134</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0686</v>
+        <v>-0.3185</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3417</v>
+        <v>-0.1949</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8249</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.396</v>
+        <v>0.5009</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5748</v>
+        <v>0.1753</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1788</v>
+        <v>0.3256</v>
       </c>
       <c r="V20" t="n">
         <v>0.3538</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1227</v>
+        <v>-1.5972</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0816</v>
+        <v>-1.4386</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0411</v>
+        <v>-0.1585</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6692</v>
@@ -2092,13 +2092,13 @@
         <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3484</v>
+        <v>0.1771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4319</v>
+        <v>0.211</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0339</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5214</v>
+        <v>-2.3301</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4693</v>
+        <v>-2.3621</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0521</v>
+        <v>0.032</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2458</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0269</v>
+        <v>-0.8356</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5702</v>
+        <v>-0.486</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6356</v>
+        <v>-3.4633</v>
       </c>
       <c r="E23" t="n">
         <v>-1.8792</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7564</v>
+        <v>-1.5841</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1737</v>
@@ -2248,13 +2248,13 @@
         <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.67</v>
+        <v>-0.4978</v>
       </c>
       <c r="T23" t="n">
         <v>-0.261</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4091</v>
+        <v>-0.2368</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.9041</v>
+        <v>7.6187</v>
       </c>
       <c r="E24" t="n">
-        <v>4.742</v>
+        <v>4.741999999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1624</v>
+        <v>2.8766</v>
       </c>
       <c r="G24" t="n">
         <v>4.4907</v>
@@ -2326,13 +2326,13 @@
         <v>15.6088</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8788</v>
+        <v>-1.1646</v>
       </c>
       <c r="T24" t="n">
         <v>2.3744</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.2532</v>
+        <v>-3.539</v>
       </c>
       <c r="V24" t="n">
         <v>2.2111</v>
